--- a/books_verified.xlsx
+++ b/books_verified.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -38,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,19 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,7 +824,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unknown Author</t>
+          <t>FAKE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -890,32 +889,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAKE BOOK TITLE 123</t>
+          <t>Cien años de soledad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown Author</t>
+          <t>Gabriel García Márquez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Realismo mágico</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not found on Wikipedia</t>
+          <t>One Hundred Years of Solitude</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://en.wikipedia.org/wiki/One_Hundred_Years_of_Solitude</t>
         </is>
       </c>
     </row>
@@ -925,30 +924,100 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>불편한 편의점</t>
+          <t>One Hundred Years of Solitude</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>김호연</t>
+          <t>Gabriel García Márquez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>힐링 소설</t>
+          <t>Magical Realism</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>One Hundred Years of Solitude</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/One_Hundred_Years_of_Solitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>채식주의자</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한강</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>문학</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>The Vegetarian</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Vegetarian</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>blahl balba hla FAKE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bla hb bl31414</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>&amp;#(*@($#df</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>NOT FOUND</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Not found on Wikipedia</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -965,84 +1034,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>BOOK VERIFICATION STATISTICS</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not Verified</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Total Books</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Proportion</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>71.43%</t>
-        </is>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Verified Books</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Not Verified Books</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Proportion Verified</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>81.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Margin of Error</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>23.66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lower Bound</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>47.76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Upper Bound</t>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.09%</t>
+          <t>±19.13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Lower Bound (95%)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>62.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Upper Bound (95%)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
         </is>
       </c>
     </row>

--- a/books_verified.xlsx
+++ b/books_verified.xlsx
@@ -27,9 +27,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
@@ -423,8 +425,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -434,7 +451,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Original Title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -454,12 +471,42 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Translated Title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Translation Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Search Title (ASCII)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Wikipedia Title</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Resolution Method</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate Group</t>
         </is>
       </c>
     </row>
@@ -469,34 +516,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>To Kill a Mockingbird</t>
+          <t>The Haunting of Hill House</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Harper Lee</t>
+          <t>Shirley Jackson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Psychological horror</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>To Kill a Mockingbird</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/To_Kill_a_Mockingbird</t>
-        </is>
-      </c>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>the haunting of hill house</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The Haunting of Hill House</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Haunting_of_Hill_House</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,34 +571,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FAKE BOOK TITLE 321</t>
+          <t>To Kill a Mockingbird</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown Author</t>
+          <t>Harper Lee</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FAKE</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Not found on Wikipedia</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>to kill a mockingbird</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To Kill a Mockingbird</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/To_Kill_a_Mockingbird</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -539,34 +626,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Great Gatsby</t>
+          <t>FAKE BOOK TITLE 321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F. Scott Fitzgerald</t>
+          <t>Unknown Author</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>FAKE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>The Great Gatsby</t>
-        </is>
-      </c>
+          <t>[NOT FOUND]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_Great_Gatsby</t>
-        </is>
-      </c>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fake book title 321</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Not found on Wikipedia</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -574,32 +681,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pride and Prejudice</t>
+          <t>One Hundred Years of Solitude</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jane Austen</t>
+          <t>Gabriel García Márquez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Romance</t>
+          <t>Magical Realism</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pride and Prejudice</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pride_and_Prejudice</t>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>one hundred years of solitude</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>One Hundred Years of Solitude</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/One_Hundred_Years_of_Solitude</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L1</t>
         </is>
       </c>
     </row>
@@ -609,34 +740,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Catcher in the Rye</t>
+          <t>战争与和平</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>J.D. Salinger</t>
+          <t>列夫·托尔斯泰</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>小说 / 历史小说</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>[VERIFIED]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The Catcher in the Rye</t>
+          <t>war and peace</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_Catcher_in_the_Rye</t>
-        </is>
-      </c>
+          <t>translated</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>war and peace</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>War and Peace</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/War_and_Peace</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -644,32 +799,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brave New World</t>
+          <t>THE LORD OF THE RINGS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aldous Huxley</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dystopian</t>
+          <t>FANTASY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Brave New World</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brave_New_World</t>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>the lord of the rings</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Lord_of_the_Rings</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L2</t>
         </is>
       </c>
     </row>
@@ -679,34 +858,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hobbit</t>
+          <t>Преступление и наказание</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Фёдор Михайлович Достоевский</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fantasy</t>
+          <t>философский роман</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>[VERIFIED]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The Hobbit</t>
+          <t>Crime and Punishment</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_Hobbit</t>
-        </is>
-      </c>
+          <t>translated</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>crime and punishment</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Crime and Punishment</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Crime_and_Punishment</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -714,34 +917,54 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harry Potter and the Philosopher's Stone</t>
+          <t>The HObBit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fantasy</t>
+          <t>FantASY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Harry Potter and the Philosopher's Stone</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Harry_Potter_and_the_Philosopher's_Stone</t>
-        </is>
-      </c>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>the hobbit</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The Hobbit</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Hobbit</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -749,34 +972,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Da Vinci Code</t>
+          <t>채식주의자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dan Brown</t>
+          <t>한강</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>문학</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>[NOT FOUND]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The Da Vinci Code</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_Da_Vinci_Code</t>
-        </is>
-      </c>
+          <t>translated</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vegetarian</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The Vegetarian</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -799,19 +1046,39 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Gone with the Wind (novel)</t>
-        </is>
-      </c>
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Gone_with_the_Wind_(novel)</t>
-        </is>
-      </c>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>gone with the wind</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Gone with the Wind (film)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gone_with_the_Wind_(film)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -819,34 +1086,54 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FAKE BOOK TITLE XYZ123</t>
+          <t>blahl balba hla FAKE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FAKE</t>
+          <t>bla hb bl31414</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>&amp;#(*@($#df</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>[NOT FOUND]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>blahl balba hla fake</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Not found on Wikipedia</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -869,17 +1156,41 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>the lord of the rings</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>The Lord of the Rings</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/The_Lord_of_the_Rings</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L2</t>
         </is>
       </c>
     </row>
@@ -904,17 +1215,45 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>[NOT FOUND]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>One hundred years of loneliness</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>translated</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>one hundred years of loneliness</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>One Hundred Years of Solitude</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/One_Hundred_Years_of_Solitude</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L1</t>
         </is>
       </c>
     </row>
@@ -939,87 +1278,41 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>[VERIFIED]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>same_text</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>one hundred years of solitude</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>One Hundred Years of Solitude</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/One_Hundred_Years_of_Solitude</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>채식주의자</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>한강</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>문학</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>The Vegetarian</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/The_Vegetarian</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>blahl balba hla FAKE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>bla hb bl31414</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>&amp;#(*@($#df</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Not found on Wikipedia</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L1</t>
         </is>
       </c>
     </row>
@@ -1034,8 +1327,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -1051,7 +1348,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1061,7 +1358,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1071,7 +1368,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1379,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81.25%</t>
+          <t>71.43%</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1391,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>±19.13%</t>
+          <t>+-23.66%</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1403,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>62.12%</t>
+          <t>47.76%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1415,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>95.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Match Confidence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>99.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gemini Calls Used</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2 / 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AI Summary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Based on these results, we can be 95% certain that the true verification rate for all such books lies between 47.8% and 95.1%.</t>
         </is>
       </c>
     </row>
